--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.9258216181704</v>
+        <v>4.86294601295269</v>
       </c>
       <c r="D2" t="n">
-        <v>29.7164853304734</v>
+        <v>4.828928866201927</v>
       </c>
       <c r="E2" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F2" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.46997081184767</v>
+        <v>3.326370256925247</v>
       </c>
       <c r="D3" t="n">
-        <v>19.86521344451738</v>
+        <v>3.228097184734075</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F3" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.66647065645756</v>
+        <v>3.845801481674354</v>
       </c>
       <c r="D4" t="n">
-        <v>23.3031206265613</v>
+        <v>3.786757101816212</v>
       </c>
       <c r="E4" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F4" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.0635721099438</v>
+        <v>9.597830467865867</v>
       </c>
       <c r="D5" t="n">
-        <v>62.10886911585384</v>
+        <v>10.09269123132625</v>
       </c>
       <c r="E5" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F5" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.56835887874706</v>
+        <v>5.454858317796398</v>
       </c>
       <c r="D6" t="n">
-        <v>35.63572443603615</v>
+        <v>5.790805220855875</v>
       </c>
       <c r="E6" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F6" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.31631068121317</v>
+        <v>6.713900485697141</v>
       </c>
       <c r="D7" t="n">
-        <v>41.97981126465469</v>
+        <v>6.821719330506387</v>
       </c>
       <c r="E7" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F7" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.53165351804673</v>
+        <v>10.32389369668259</v>
       </c>
       <c r="D8" t="n">
-        <v>66.03381943440878</v>
+        <v>10.73049565809143</v>
       </c>
       <c r="E8" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F8" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.14435622894803</v>
+        <v>7.010957887204055</v>
       </c>
       <c r="D9" t="n">
-        <v>45.55058342881087</v>
+        <v>7.401969807181767</v>
       </c>
       <c r="E9" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F9" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.09121898068811</v>
+        <v>7.002323084361818</v>
       </c>
       <c r="D10" t="n">
-        <v>44.62877729876117</v>
+        <v>7.25217631104869</v>
       </c>
       <c r="E10" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F10" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.17853149221816</v>
+        <v>4.091511367485451</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7349527942446</v>
+        <v>4.181929829064748</v>
       </c>
       <c r="E11" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F11" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.33252114677153</v>
+        <v>5.416534686350373</v>
       </c>
       <c r="D12" t="n">
-        <v>34.24004965091349</v>
+        <v>5.564008068273442</v>
       </c>
       <c r="E12" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F12" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.17227070443426</v>
+        <v>6.527993989470568</v>
       </c>
       <c r="D13" t="n">
-        <v>60.24431952340713</v>
+        <v>9.789701922553659</v>
       </c>
       <c r="E13" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F13" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.30210270839112</v>
+        <v>5.574091690113558</v>
       </c>
       <c r="D14" t="n">
-        <v>52.4348179757932</v>
+        <v>8.520657921066396</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F14" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.97156504654419</v>
+        <v>5.19537932006343</v>
       </c>
       <c r="D15" t="n">
-        <v>30.2248836544392</v>
+        <v>4.911543593846369</v>
       </c>
       <c r="E15" t="n">
-        <v>11.92621617858904</v>
+        <v>1.938010129020719</v>
       </c>
       <c r="F15" t="n">
-        <v>14.43855816958943</v>
+        <v>2.346265702558282</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
